--- a/regressoes/cdx_us_hy/outputs/CDX_US_HY_spread_simple_analysis.xlsx
+++ b/regressoes/cdx_us_hy/outputs/CDX_US_HY_spread_simple_analysis.xlsx
@@ -16,10 +16,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="292">
   <si>
-    <t>series (m/y)</t>
-  </si>
-  <si>
-    <t>start (m/y)</t>
+    <t>series start (m/y)</t>
+  </si>
+  <si>
+    <t>sample start (m/y)</t>
   </si>
   <si>
     <t>last (m/y)</t>
